--- a/sheets/조재수대금교본/검수/화류춘몽.xlsx
+++ b/sheets/조재수대금교본/검수/화류춘몽.xlsx
@@ -2636,8 +2636,7 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="E5" s="23"/>
@@ -2651,14 +2650,14 @@
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–И</t>
+–</t>
         </is>
       </c>
       <c r="I5" s="23"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-–И</t>
+–</t>
         </is>
       </c>
       <c r="K5" s="23"/>
@@ -2674,7 +2673,7 @@
       <c r="C6" s="24"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應ʒ
+          <t xml:space="preserve">應
 淋仲</t>
         </is>
       </c>
@@ -2687,16 +2686,14 @@
       <c r="G6" s="24"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="I6" s="24"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="K6" s="24"/>
@@ -2742,8 +2739,7 @@
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="G8" s="23"/>
@@ -2802,8 +2798,7 @@
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="G10" s="24"/>
@@ -2851,19 +2846,14 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D12" s="21"/>
       <c r="E12" s="23"/>
       <c r="F12" s="21"/>
       <c r="G12" s="23"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="I12" s="23"/>
@@ -2906,11 +2896,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21"/>
       <c r="G14" s="24"/>
@@ -2965,8 +2951,7 @@
       <c r="C16" s="23"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E16" s="23"/>
@@ -2989,8 +2974,7 @@
       <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="E17" s="23"/>
@@ -3012,7 +2996,7 @@
       <c r="C18" s="24"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應ʒ
+          <t xml:space="preserve">應
 林仲</t>
         </is>
       </c>
@@ -3020,8 +3004,7 @@
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="G18" s="24"/>

--- a/sheets/조재수대금교본/검수/화류춘몽.xlsx
+++ b/sheets/조재수대금교본/검수/화류춘몽.xlsx
@@ -2650,14 +2650,14 @@
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–</t>
+–И</t>
         </is>
       </c>
       <c r="I5" s="23"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-–</t>
+–И</t>
         </is>
       </c>
       <c r="K5" s="23"/>
@@ -2673,7 +2673,7 @@
       <c r="C6" s="24"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
+          <t xml:space="preserve">應ʒ
 淋仲</t>
         </is>
       </c>
@@ -2951,7 +2951,8 @@
       <c r="C16" s="23"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="E16" s="23"/>
@@ -2996,7 +2997,7 @@
       <c r="C18" s="24"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
+          <t xml:space="preserve">應ʒ
 林仲</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/화류춘몽.xlsx
+++ b/sheets/조재수대금교본/검수/화류춘몽.xlsx
@@ -2536,22 +2536,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="61.54" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="68.7" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="68.7" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="68.7" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="68.7" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="K6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="68.7" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="68.7" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="68.7" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="68.7" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -2811,7 +2811,7 @@
       <c r="J10" s="21"/>
       <c r="K10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="68.7" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="68.7" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="68.7" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="68.7" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="K14" s="24"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="68.7" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="68.7" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -2968,7 +2968,7 @@
       <c r="J16" s="21"/>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="68.7" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2991,7 +2991,7 @@
       <c r="J17" s="21"/>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="68.7" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -3030,6 +3030,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="65"/>
 </worksheet>
 </file>